--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
